--- a/docs/n90-kvm-host/lmbench-N10-4config.xlsx
+++ b/docs/n90-kvm-host/lmbench-N10-4config.xlsx
@@ -2555,7 +2555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2592,306 +2592,318 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>results/n90-day3/n90-{kvmoff,nvhe,vhe,pkvm}-noLSM-full-cpu0.csv</t>
+          <t>results/n90-day3-host/n90-{kvmoff,nvhe,vhe,pkvm}-noLSM-full-cpu0.csv</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>每个配置 iter 数</t>
+          <t>lat_mmap 高精度覆盖</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N=10</t>
+          <t>results/precise-mmap/*.log 覆盖 0.5/1/2/4/8/16/64 MB 行</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>CPU 频率</t>
+          <t>每个配置 iter 数</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>锁 1900 MHz, governor=performance</t>
+          <t>N=10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>LSM 栈</t>
+          <t>CPU 频率</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>capability,kycp（无 ksaf/bpf/audit）</t>
+          <t>锁 1900 MHz, governor=performance</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>THP</t>
+          <t>LSM 栈</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>capability,kycp（无 ksaf/bpf/audit）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>ASLR</t>
+          <t>THP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>never</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>绑核</t>
+          <t>ASLR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cpu0 (taskset -c 0)</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>lmbench config</t>
+          <t>绑核</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONFIG.host（全套 BENCHMARK_*=YES）</t>
+          <t>cpu0 (taskset -c 0)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>lmbench config</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CONFIG.host（全套 BENCHMARK_*=YES）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
           <t>噪声抑制</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>72 项系统 + 12 项用户 systemd 服务 mask，桌面 multi-user.target</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Sheet 说明：</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Highlights</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>论文表 (Sci China Inf Sci) 30+ 项 + lat_mmap/mem hierarchy/bw 重点</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  All metrics</t>
+          <t xml:space="preserve">  Highlights</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>全部 684 项 (bench, variant) 中位 + MAD% + 5 个跨配置 Δ%</t>
+          <t>论文表 (Sci China Inf Sci) 30+ 项 + lat_mmap/mem hierarchy/bw 重点</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">  All metrics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>全部 684 项 (bench, variant) 中位 + MAD% + 5 个跨配置 Δ%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Per-iter raw</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>论文重点项的 10 个 iter 单值（用于自己重新算 stat）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>论文重点项的 10 个 iter 单值 + 中位/MAD%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Δ% 颜色编码（方向 × 强度）：</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  方向（按指标单位判断）：</t>
-        </is>
-      </c>
+      <c r="A21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    单位 us / ns（延迟）</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>负 Δ% → 更快 → 绿；正 Δ% → 更慢 → 红</t>
+          <t xml:space="preserve">  方向（按指标单位判断）：</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    单位 MB/s（带宽）</t>
+          <t xml:space="preserve">    单位 us / ns（延迟）</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>正 Δ% → 更高 → 绿；负 Δ% → 更低 → 红</t>
+          <t>负 Δ% → 更快 → 绿；正 Δ% → 更慢 → 红</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">    单位 MB/s（带宽）</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>正 Δ% → 更高 → 绿；负 Δ% → 更低 → 红</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">    单位 pages（TLB）</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>正 Δ% → 更大 → 绿；负 Δ% → 更小 → 红</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  强度：</t>
-        </is>
-      </c>
+      <c r="A26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    |Δ| &gt; 10%</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>深色 + 粗体（显著差异）</t>
+          <t xml:space="preserve">  强度：</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5% &lt; |Δ| ≤ 10%</t>
+          <t xml:space="preserve">    |Δ| &gt; 10%</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中等色</t>
+          <t>深色 + 粗体（显著差异）</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2% &lt; |Δ| ≤ 5%</t>
+          <t xml:space="preserve">    5% &lt; |Δ| ≤ 10%</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>浅色</t>
+          <t>中等色</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
+          <t xml:space="preserve">    2% &lt; |Δ| ≤ 5%</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>浅色</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
           <t xml:space="preserve">    |Δ| ≤ 2%</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>黑色（在 MAD 噪声范围内，不算差异）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr"/>
-    </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>关键 finding：</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. host syscall fastpath 4 模式无差（≤ 1%）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. CPU 算术 4 模式绝对相等（sanity ✓）</t>
+          <t xml:space="preserve">  1. host syscall fastpath 4 模式无差（≤ 1%）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. pkvm 在 lat_mmap 大段比其它 3 模式慢 +15-42%（stage-2 表维护）</t>
+          <t xml:space="preserve">  2. CPU 算术 4 模式绝对相等（sanity ✓）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. host EL2 (vhe) vs host EL1 (kvmoff/nvhe) 无可观测性能差</t>
+          <t xml:space="preserve">  3. pkvm 在 lat_mmap 大段比其它 3 模式慢 +15-42%（stage-2 表维护）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. host EL2 (vhe) vs host EL1 (kvmoff/nvhe) 无可观测性能差</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. TLB / cache 层级 / bw_mem 4 模式相等</t>
         </is>
